--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
   <si>
     <t>calcula_modernidad_base_RETRO_altas</t>
   </si>
@@ -70,14 +70,25 @@
   </si>
   <si>
     <t>set @porc_mod_colec=1</t>
+  </si>
+  <si>
+    <t>Nombre haber</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -120,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -133,6 +144,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M26"/>
+  <dimension ref="A2:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" customWidth="1"/>
@@ -439,50 +453,19 @@
     <col min="14" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:13">
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="25.5" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="18" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>460</v>
-      </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -494,12 +477,10 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
+    <row r="5" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="2"/>
@@ -513,10 +494,12 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
+    <row r="6" spans="1:13" ht="18" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
+        <v>460</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
@@ -531,9 +514,11 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="2"/>
@@ -547,10 +532,13 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -561,10 +549,13 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -575,19 +566,10 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="10" spans="1:13">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -598,19 +580,10 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2">
-        <v>480</v>
-      </c>
-      <c r="C11" s="2">
-        <v>480</v>
-      </c>
-      <c r="D11" s="2">
-        <v>460</v>
-      </c>
+    <row r="11" spans="1:13">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -621,18 +594,18 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="28.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -644,16 +617,18 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
+    <row r="13" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2">
+        <v>480</v>
+      </c>
+      <c r="C13" s="2">
+        <v>480</v>
+      </c>
+      <c r="D13" s="2">
+        <v>460</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -666,9 +641,18 @@
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -680,9 +664,16 @@
       <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -694,14 +685,9 @@
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -713,14 +699,9 @@
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2">
-        <v>500</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -733,17 +714,13 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -755,21 +732,37 @@
       <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="4"/>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2">
+        <v>500</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -781,28 +774,21 @@
       <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -814,20 +800,26 @@
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="2">
-        <v>320</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="1"/>
@@ -841,24 +833,22 @@
       <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="4"/>
-      <c r="B25" s="2"/>
+      <c r="A25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2">
+        <v>320</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -868,6 +858,35 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
